--- a/pentest-ornek-beyanname.xlsx
+++ b/pentest-ornek-beyanname.xlsx
@@ -770,10 +770,10 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>2201</v>
+        <v>1105</v>
       </c>
       <c r="D8" t="n">
         <v>2320</v>
@@ -813,10 +813,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>2201</v>
+        <v>1105</v>
       </c>
       <c r="D9" t="n">
         <v>2320</v>
@@ -856,10 +856,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>4703</v>
+        <v>1108</v>
       </c>
       <c r="D10" t="n">
         <v>2320</v>
@@ -899,10 +899,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>4703</v>
+        <v>1108</v>
       </c>
       <c r="D11" t="n">
         <v>2320</v>
@@ -942,10 +942,10 @@
         <v>8</v>
       </c>
       <c r="B12" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>6801</v>
+        <v>1306</v>
       </c>
       <c r="D12" t="n">
         <v>2320</v>
@@ -985,10 +985,10 @@
         <v>8</v>
       </c>
       <c r="B13" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>6801</v>
+        <v>1306</v>
       </c>
       <c r="D13" t="n">
         <v>2320</v>
